--- a/artfynd/S 422-2026 artfynd.xlsx
+++ b/artfynd/S 422-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -907,32 +907,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134869025</v>
+        <v>137414427</v>
       </c>
       <c r="B4" t="n">
-        <v>56896</v>
+        <v>8383</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208257</v>
+        <v>106540</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Anguis fragilis</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -940,21 +940,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Backebo, Backebo, Ög</t>
+          <t>Backebo, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>494554</v>
+        <v>494446</v>
       </c>
       <c r="R4" t="n">
-        <v>6493861</v>
+        <v>6493942</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -981,22 +977,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,6 +1017,127 @@
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137414427</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>134869025</v>
+      </c>
+      <c r="B5" t="n">
+        <v>56896</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>208257</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kopparödla</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Anguis fragilis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Backebo, Backebo, Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>494554</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6493861</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Pia Georgsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Pia Georgsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/134869025</t>
         </is>
@@ -1031,6 +1148,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
